--- a/backend/elderlycare-common/src/main/resources/excel_model/CustomerManagement.xlsx
+++ b/backend/elderlycare-common/src/main/resources/excel_model/CustomerManagement.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -463,7 +463,6 @@
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -512,11 +511,6 @@
           <t>是否入住</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -564,11 +558,6 @@
           <t>checkedIn</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>operation</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -612,11 +601,6 @@
           <t>已入住</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>查看/编辑</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -660,11 +644,6 @@
           <t>已入住</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>查看/编辑</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -708,11 +687,6 @@
       <c r="I5" s="2" t="inlineStr">
         <is>
           <t>未入住</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>查看/编辑</t>
         </is>
       </c>
     </row>
